--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260709.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260709.xlsx
@@ -931,17 +931,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>64,710,000</t>
+          <t>209,210,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>209,210,000</t>
+          <t>64,710,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>潤弘</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>14,250,000</t>
+          <t>41,370,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>潤弘</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>41,370,000</t>
+          <t>14,250,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
